--- a/DATA/MASTER/C10_MASTER/Estadisticas_Descriptivas_Dataset_Maestro_Framework_v04.xlsx
+++ b/DATA/MASTER/C10_MASTER/Estadisticas_Descriptivas_Dataset_Maestro_Framework_v04.xlsx
@@ -1018,47 +1018,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>528</v>
+        <v>336</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>63.64</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08333333333333333</v>
+        <v>437503454.9203588</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>432174766.3366481</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2766475001553201</v>
+        <v>93579100.66875789</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07653383934218785</v>
+        <v>8757048081973523</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>290141870.9677419</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>356941398.2142857</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>501304870.967742</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>619585580.6451613</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="O12" t="n">
-        <v>331.98</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="13">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1082,34 +1082,34 @@
         <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>0.09090909090909091</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2877524092433606</v>
+        <v>2.411736011307066</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08280144902535849</v>
+        <v>5.816470588235317</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="O13" t="n">
-        <v>316.53</v>
+        <v>92.76000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1133,33 +1133,35 @@
         <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>61680.56818181818</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>37972.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>53355.79201809023</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2846840541.877701</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>18810</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>26834.75</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>73342.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>163306</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="O14" t="n">
+        <v>86.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1169,7 +1171,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1182,34 +1184,34 @@
         <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6363636363636364</v>
+        <v>744.9050000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>447.33</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4815018767055868</v>
+        <v>756.0347719255574</v>
       </c>
       <c r="I15" t="n">
-        <v>0.231844057271002</v>
+        <v>571588.5763605296</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>213.66</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>991.5175</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2148.76</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="O15" t="n">
-        <v>75.66</v>
+        <v>101.49</v>
       </c>
     </row>
     <row r="16">
@@ -1271,7 +1273,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1284,34 +1286,34 @@
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6363636363636364</v>
+        <v>97.76886363636365</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4815018767055868</v>
+        <v>4.345364717909688</v>
       </c>
       <c r="I17" t="n">
-        <v>0.231844057271002</v>
+        <v>18.88219453165434</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>99.77500000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>75.66</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="18">
@@ -1322,7 +1324,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1335,34 +1337,34 @@
         <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6363636363636364</v>
+        <v>93.17750000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4815018767055868</v>
+        <v>14.77326198371468</v>
       </c>
       <c r="I18" t="n">
-        <v>0.231844057271002</v>
+        <v>218.2492696394695</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>25.38</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>90.72</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O18" t="n">
-        <v>75.66</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="19">
@@ -1373,7 +1375,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1386,34 +1388,34 @@
         <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6363636363636364</v>
+        <v>99.81818181818181</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4815018767055868</v>
+        <v>0.3860603686544951</v>
       </c>
       <c r="I19" t="n">
-        <v>0.231844057271002</v>
+        <v>0.1490426082456447</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N19" t="n">
         <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>75.66</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="20">
@@ -1424,7 +1426,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1437,34 +1439,34 @@
         <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6363636363636364</v>
+        <v>95.31818181818181</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4815018767055868</v>
+        <v>7.705507709415291</v>
       </c>
       <c r="I20" t="n">
-        <v>0.231844057271002</v>
+        <v>59.37484905985848</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>94.75</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>75.66</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="21">
@@ -1475,7 +1477,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1488,34 +1490,34 @@
         <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6363636363636364</v>
+        <v>87.68272727272726</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>84.31</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4815018767055868</v>
+        <v>9.050923702713854</v>
       </c>
       <c r="I21" t="n">
-        <v>0.231844057271002</v>
+        <v>81.91921987234747</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>60.54</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>98.02250000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O21" t="n">
-        <v>75.66</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="22">
@@ -1526,7 +1528,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1539,34 +1541,34 @@
         <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6363636363636364</v>
+        <v>45.10272727272728</v>
       </c>
       <c r="G22" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="H22" t="n">
+        <v>26.8976797343296</v>
+      </c>
+      <c r="I22" t="n">
+        <v>723.4851750905655</v>
+      </c>
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="H22" t="n">
-        <v>0.4815018767055868</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.231844057271002</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>29.02</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>63.3025</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O22" t="n">
-        <v>75.66</v>
+        <v>59.64</v>
       </c>
     </row>
     <row r="23">
